--- a/data/trans_camb/IP42B-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP42B-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 31,22</t>
+          <t>-11,65; 32,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-39,91; -2,35</t>
+          <t>-37,76; -2,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,03; 21,57</t>
+          <t>-16,34; 23,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-31,6; 6,88</t>
+          <t>-29,04; 6,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 20,22</t>
+          <t>-7,97; 20,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-28,73; -2,53</t>
+          <t>-28,98; -3,68</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,58; 158,43</t>
+          <t>-27,89; 177,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-88,95; -4,51</t>
+          <t>-87,73; -0,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-53,66; 190,99</t>
+          <t>-47,66; 224,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-87,06; 93,18</t>
+          <t>-84,53; 90,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,21; 109,73</t>
+          <t>-24,14; 116,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,0; -7,92</t>
+          <t>-80,78; -12,88</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 13,85</t>
+          <t>2,64; 13,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 9,15</t>
+          <t>-0,35; 9,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 13,22</t>
+          <t>1,8; 13,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 5,91</t>
+          <t>-3,41; 5,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,65; 11,85</t>
+          <t>3,31; 11,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 5,83</t>
+          <t>-0,62; 5,88</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,52; 979,66</t>
+          <t>24,31; 886,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,73; 630,25</t>
+          <t>-15,43; 738,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,7; 464,71</t>
+          <t>16,99; 437,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-47,81; 197,03</t>
+          <t>-43,29; 197,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,86; 402,27</t>
+          <t>38,76; 407,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,16; 194,12</t>
+          <t>-12,93; 206,4</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 13,19</t>
+          <t>-19,05; 14,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,28; 8,38</t>
+          <t>-19,71; 8,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 11,63</t>
+          <t>-7,98; 11,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 11,68</t>
+          <t>-7,71; 12,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 8,11</t>
+          <t>-8,48; 8,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 7,31</t>
+          <t>-9,4; 8,43</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>-84,0; 517,03</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-73,63; 301,71</t>
+          <t>-77,19; 350,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-74,58; 233,57</t>
+          <t>-71,06; 315,45</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 12,94</t>
+          <t>0,77; 12,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 3,78</t>
+          <t>-5,82; 4,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 12,01</t>
+          <t>1,41; 12,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 4,26</t>
+          <t>-4,3; 4,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,55; 10,42</t>
+          <t>2,82; 10,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 3,09</t>
+          <t>-3,69; 3,22</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,9; 202,66</t>
+          <t>5,64; 216,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-50,08; 61,13</t>
+          <t>-46,56; 78,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,6; 221,98</t>
+          <t>9,34; 232,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-43,68; 85,14</t>
+          <t>-41,96; 104,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,3; 168,19</t>
+          <t>27,35; 163,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-38,31; 49,73</t>
+          <t>-35,4; 49,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP42B-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP42B-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 32,39</t>
+          <t>-14,48; 31,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-37,76; -2,11</t>
+          <t>-39,69; -1,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,34; 23,44</t>
+          <t>-17,21; 22,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-29,04; 6,75</t>
+          <t>-29,59; 6,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 20,59</t>
+          <t>-10,09; 19,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-28,98; -3,68</t>
+          <t>-28,92; -2,21</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-27,89; 177,64</t>
+          <t>-32,69; 182,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-87,73; -0,41</t>
+          <t>-89,3; -2,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-47,66; 224,64</t>
+          <t>-51,05; 223,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-84,53; 90,94</t>
+          <t>-87,37; 76,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,14; 116,33</t>
+          <t>-28,72; 103,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,78; -12,88</t>
+          <t>-80,0; -8,71</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 13,83</t>
+          <t>2,63; 13,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 9,34</t>
+          <t>-0,04; 9,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 13,42</t>
+          <t>1,87; 13,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 5,7</t>
+          <t>-3,52; 6,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 11,78</t>
+          <t>3,54; 11,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 5,88</t>
+          <t>-0,9; 5,79</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,31; 886,43</t>
+          <t>28,25; 1318,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,43; 738,75</t>
+          <t>-11,0; 841,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,99; 437,71</t>
+          <t>6,12; 429,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,29; 197,64</t>
+          <t>-43,2; 239,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,76; 407,34</t>
+          <t>52,11; 394,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 206,4</t>
+          <t>-17,25; 195,69</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-19,05; 14,06</t>
+          <t>-18,46; 13,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,71; 8,78</t>
+          <t>-20,12; 7,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 11,75</t>
+          <t>-10,09; 11,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 12,0</t>
+          <t>-8,85; 10,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 8,99</t>
+          <t>-9,07; 8,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 8,43</t>
+          <t>-9,03; 7,14</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-84,0; 517,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>-90,71; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-77,19; 350,88</t>
+          <t>-76,9; 275,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,06; 315,45</t>
+          <t>-72,3; 222,62</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 12,58</t>
+          <t>0,43; 12,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 4,45</t>
+          <t>-5,84; 4,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 12,11</t>
+          <t>1,31; 12,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 4,65</t>
+          <t>-4,39; 4,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 10,81</t>
+          <t>2,55; 10,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 3,22</t>
+          <t>-4,04; 2,78</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,64; 216,23</t>
+          <t>1,69; 193,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-46,56; 78,74</t>
+          <t>-48,64; 80,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,34; 232,08</t>
+          <t>10,13; 241,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-41,96; 104,87</t>
+          <t>-43,95; 93,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,35; 163,49</t>
+          <t>24,33; 172,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-35,4; 49,55</t>
+          <t>-38,64; 44,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP42B-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP42B-Estudios-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,96</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-9,75</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>10,09</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-19,9</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,96</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-9,75</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 31,49</t>
+          <t>-16,03; 21,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-39,69; -1,51</t>
+          <t>-31,6; 6,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,21; 22,31</t>
+          <t>-13,26; 31,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-29,59; 6,81</t>
+          <t>-39,91; -2,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 19,98</t>
+          <t>-10,53; 20,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-28,92; -2,21</t>
+          <t>-28,73; -2,53</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18,35%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-45,15%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>31,54%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-62,18%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>18,35%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-45,15%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-32,69; 182,1</t>
+          <t>-53,66; 190,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-89,3; -2,81</t>
+          <t>-87,06; 93,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-51,05; 223,24</t>
+          <t>-30,58; 158,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-87,37; 76,59</t>
+          <t>-88,95; -4,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,72; 103,96</t>
+          <t>-29,21; 109,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,0; -8,71</t>
+          <t>-80,0; -7,92</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,47</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,29</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>7,84</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>4,22</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7,47</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,29</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 13,99</t>
+          <t>2,24; 13,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 9,26</t>
+          <t>-3,71; 5,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 13,48</t>
+          <t>2,72; 13,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 6,09</t>
+          <t>-0,37; 9,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 11,65</t>
+          <t>3,65; 11,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 5,79</t>
+          <t>-0,99; 5,83</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>137,82%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23,8%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>217,83%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>117,18%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>137,82%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23,8%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,25; 1318,23</t>
+          <t>18,7; 464,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 841,94</t>
+          <t>-47,81; 197,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,12; 429,8</t>
+          <t>29,52; 979,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,2; 239,72</t>
+          <t>-19,73; 630,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,11; 394,39</t>
+          <t>52,86; 402,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 195,69</t>
+          <t>-22,16; 194,12</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,66</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,62</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-0,68</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-3,49</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,66</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,62</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 13,6</t>
+          <t>-9,13; 11,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,12; 7,95</t>
+          <t>-7,95; 11,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 11,15</t>
+          <t>-20,34; 13,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 10,69</t>
+          <t>-21,28; 8,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 8,67</t>
+          <t>-8,31; 8,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 7,14</t>
+          <t>-9,09; 7,31</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>13,12%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>51,93%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-6,02%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-30,68%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>13,12%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>51,93%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-90,71; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-76,9; 275,02</t>
+          <t>-73,63; 301,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-72,3; 222,62</t>
+          <t>-74,58; 233,57</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6,72</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,17</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>6,61</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-0,76</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>6,72</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 12,48</t>
+          <t>1,05; 12,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 4,53</t>
+          <t>-4,21; 4,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 12,76</t>
+          <t>0,68; 12,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 4,38</t>
+          <t>-5,97; 3,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,55; 10,68</t>
+          <t>2,55; 10,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 2,78</t>
+          <t>-3,99; 3,09</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>91,85%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>71,93%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-8,26%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>91,85%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,69; 193,66</t>
+          <t>5,6; 221,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-48,64; 80,72</t>
+          <t>-43,68; 85,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,13; 241,51</t>
+          <t>3,9; 202,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-43,95; 93,75</t>
+          <t>-50,08; 61,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,33; 172,16</t>
+          <t>20,3; 168,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-38,64; 44,13</t>
+          <t>-38,31; 49,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP42B-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP42B-Estudios-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -118,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -591,467 +600,319 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3,96</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-9,75</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10,09</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-19,9</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,88</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-15,11</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>3.962398759314387</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-9.74959092335698</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>10.09420579838595</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-19.9007787616966</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>5.884630425863008</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-15.10575792567513</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-16,03; 21,57</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-31,6; 6,88</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-13,26; 31,22</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-39,91; -2,35</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-10,53; 20,22</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-28,73; -2,53</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-16.02794720361817</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-31.60358209068584</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-13.26473488830202</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-39.90797625741831</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-10.53375312185728</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-28.73474786662029</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>18,35%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-45,15%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>31,54%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-62,18%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>21,73%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-55,78%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>21.56675873258787</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.878426426818961</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>31.21908316694225</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>-2.347261634003118</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>20.21503586745917</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>-2.529128530569346</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-53,66; 190,99</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-87,06; 93,18</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-30,58; 158,43</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-88,95; -4,51</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-29,21; 109,73</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-80,0; -7,92</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0.183491057745812</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.4514847847936648</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.3153846638937752</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.6217824905041711</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.2173135585712337</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.5578406411584732</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>7,47</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,29</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7,84</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,22</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,57</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,62</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>-0.5366007774099716</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.8706326359114901</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.3057943377775254</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.8894750782749047</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.2921213055778496</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.8000007957780053</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>2,24; 13,22</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,71; 5,91</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2,72; 13,85</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-0,37; 9,15</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>3,65; 11,85</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-0,99; 5,83</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>1.909861183444912</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.9318318301499209</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1.584318745860282</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-0.04506321189522615</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.09733554620505</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-0.0791541723500776</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>137,82%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>23,8%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>217,83%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>117,18%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>165,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>57,13%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>7.469592825211965</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.290174719438453</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>7.841963256827436</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>4.218409313818609</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>7.573327002801711</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>2.622012428985524</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>18,7; 464,71</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-47,81; 197,03</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>29,52; 979,66</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-19,73; 630,25</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>52,86; 402,27</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-22,16; 194,12</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>2.237953022164372</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.70505059935763</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>2.715731920579284</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-0.3650321120425175</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>3.654967948330125</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.9947407945662585</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,66</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2,62</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,68</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,49</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,36</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>13.22340031960404</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.910954166889888</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>13.8477954398518</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>9.152924577301054</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>11.84759833322948</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>5.830130046310757</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-9,13; 11,63</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-7,95; 11,68</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-20,34; 13,19</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-21,28; 8,38</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-8,31; 8,11</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-9,09; 7,31</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>1.378195715221679</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.2380468804425026</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>2.178296735540784</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1.171766168308141</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>1.649988918329625</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.5712537501613451</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>13,12%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>51,93%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-6,02%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-30,68%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0.1869926234743743</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.4781270828424949</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0.2951985060830163</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.197257723875169</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0.5285784217630617</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2216325986773582</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-73,63; 301,71</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-74,58; 233,57</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>4.647072298344018</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>1.970269959759652</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>9.796572735627626</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>6.302530950052457</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>4.022694192085683</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.941203727910255</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,153 +920,301 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>6,72</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>6,61</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,76</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,72</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-0,25</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>0.6627939644145833</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2.623960490874242</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.6845621778301836</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-3.48815622872445</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.3642868673791377</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0.1524762589585629</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>1,05; 12,01</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-4,21; 4,26</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0,68; 12,94</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-5,97; 3,78</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2,55; 10,42</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-3,99; 3,09</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-9.134744009240116</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-7.949089675715866</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-20.34158609596527</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-21.28120156869571</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-8.305339395242889</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-9.090704131727698</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>91,85%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>71,93%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-8,26%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>82,21%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-3,05%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>11.63419488094484</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>11.67754546170168</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>13.18948451097521</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>8.382403528706901</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>8.113239386953595</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>7.313220936582409</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>5,6; 221,98</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-43,68; 85,14</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>3,9; 202,66</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-50,08; 61,13</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>20,3; 168,19</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-38,31; 49,73</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>0.131183700642958</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.5193481926737683</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.06021368839453107</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.3068161797860224</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.0477898944477311</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.02000298384028966</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="n">
+        <v>-0.7363218758758238</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.7457914809281547</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="n">
+        <v>3.017127024623373</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>2.335671212403414</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>6.720261215193377</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.173549122744468</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>6.607465645356942</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.7586609906772096</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>6.719489416295228</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-0.2494334140975704</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>1.047178754286258</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-4.207019312805564</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.6780867774287473</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-5.969087848297798</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>2.547116440098311</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-3.985820554176263</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>12.00562830054263</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>4.256553015069088</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>12.94045365542097</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>3.777678930353857</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>10.41607911552826</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>3.092960600540049</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>0.9185142067132207</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.02372040754056067</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.7193091833090888</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.08259018614738602</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.8221383033749753</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.03051850388719985</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>0.05602297857663513</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.4367745408595781</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>0.03899298249586584</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.5007975681671342</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0.202951562239883</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.3831066098721616</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>2.219838037073243</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.8513796672825686</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>2.026594213138856</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.611265853252044</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>1.681850657242752</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.4973003595448299</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1213,14 +1222,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
